--- a/resources/templates/standard/A5100-03.xlsx
+++ b/resources/templates/standard/A5100-03.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="70">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>내부 감사 보고서 (갑)</t>
   </si>
@@ -1061,12 +1064,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -1088,21 +1093,21 @@
       <c r="W1" s="2"/>
       <c r="X1" s="2"/>
       <c r="Y1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z1" s="3"/>
       <c r="AA1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB1" s="4"/>
       <c r="AC1" s="4"/>
       <c r="AD1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE1" s="4"/>
       <c r="AF1" s="4"/>
       <c r="AG1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH1" s="4"/>
       <c r="AI1" s="4"/>
@@ -1141,7 +1146,7 @@
       <c r="AE2" s="6"/>
       <c r="AF2" s="7"/>
       <c r="AG2" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH2" s="6"/>
       <c r="AI2" s="8"/>
@@ -1185,7 +1190,7 @@
     </row>
     <row r="4" ht="17.1" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1200,7 +1205,7 @@
       <c r="L4" s="14"/>
       <c r="M4" s="14"/>
       <c r="N4" s="15" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O4" s="15"/>
       <c r="P4" s="15"/>
@@ -1214,14 +1219,14 @@
       <c r="X4" s="16"/>
       <c r="Y4" s="16"/>
       <c r="Z4" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA4" s="15"/>
       <c r="AB4" s="15"/>
       <c r="AC4" s="15"/>
       <c r="AD4" s="15"/>
       <c r="AE4" s="16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF4" s="16"/>
       <c r="AG4" s="16"/>
@@ -1230,7 +1235,7 @@
     </row>
     <row r="5" ht="17.1" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="17"/>
       <c r="C5" s="17"/>
@@ -1245,7 +1250,7 @@
       <c r="L5" s="18"/>
       <c r="M5" s="18"/>
       <c r="N5" s="19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O5" s="19"/>
       <c r="P5" s="19"/>
@@ -1259,14 +1264,14 @@
       <c r="X5" s="18"/>
       <c r="Y5" s="18"/>
       <c r="Z5" s="19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA5" s="19"/>
       <c r="AB5" s="19"/>
       <c r="AC5" s="19"/>
       <c r="AD5" s="19"/>
       <c r="AE5" s="18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF5" s="18"/>
       <c r="AG5" s="18"/>
@@ -1275,7 +1280,7 @@
     </row>
     <row r="6" ht="17.1" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
@@ -1283,7 +1288,7 @@
       <c r="E6" s="17"/>
       <c r="F6" s="17"/>
       <c r="G6" s="18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H6" s="18"/>
       <c r="I6" s="18"/>
@@ -1292,7 +1297,7 @@
       <c r="L6" s="18"/>
       <c r="M6" s="18"/>
       <c r="N6" s="19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O6" s="19"/>
       <c r="P6" s="19"/>
@@ -1318,7 +1323,7 @@
     </row>
     <row r="7" ht="17.1" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" s="21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" s="21"/>
       <c r="C7" s="21"/>
@@ -1326,7 +1331,7 @@
       <c r="E7" s="21"/>
       <c r="F7" s="21"/>
       <c r="G7" s="22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H7" s="22"/>
       <c r="I7" s="22"/>
@@ -1359,10 +1364,10 @@
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" s="23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" s="24"/>
       <c r="D8" s="24"/>
@@ -1402,10 +1407,10 @@
       <c r="A9" s="26"/>
       <c r="B9" s="27"/>
       <c r="C9" s="24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E9" s="24"/>
       <c r="F9" s="24"/>
@@ -1430,7 +1435,7 @@
       <c r="Y9" s="24"/>
       <c r="Z9" s="24"/>
       <c r="AA9" s="27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB9" s="24"/>
       <c r="AC9" s="24"/>
@@ -1445,10 +1450,10 @@
       <c r="A10" s="26"/>
       <c r="B10" s="27"/>
       <c r="C10" s="24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E10" s="28"/>
       <c r="F10" s="24"/>
@@ -1473,7 +1478,7 @@
       <c r="Y10" s="24"/>
       <c r="Z10" s="24"/>
       <c r="AA10" s="27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB10" s="24"/>
       <c r="AC10" s="24"/>
@@ -1488,10 +1493,10 @@
       <c r="A11" s="26"/>
       <c r="B11" s="27"/>
       <c r="C11" s="24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E11" s="28"/>
       <c r="F11" s="24"/>
@@ -1516,7 +1521,7 @@
       <c r="Y11" s="24"/>
       <c r="Z11" s="24"/>
       <c r="AA11" s="27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB11" s="24"/>
       <c r="AC11" s="24"/>
@@ -1531,10 +1536,10 @@
       <c r="A12" s="26"/>
       <c r="B12" s="27"/>
       <c r="C12" s="24" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E12" s="28"/>
       <c r="F12" s="24"/>
@@ -1559,7 +1564,7 @@
       <c r="Y12" s="24"/>
       <c r="Z12" s="24"/>
       <c r="AA12" s="27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB12" s="24"/>
       <c r="AC12" s="24"/>
@@ -1574,10 +1579,10 @@
       <c r="A13" s="26"/>
       <c r="B13" s="27"/>
       <c r="C13" s="24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E13" s="24"/>
       <c r="F13" s="24"/>
@@ -1602,7 +1607,7 @@
       <c r="Y13" s="24"/>
       <c r="Z13" s="24"/>
       <c r="AA13" s="27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB13" s="24"/>
       <c r="AC13" s="24"/>
@@ -1652,7 +1657,7 @@
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A15" s="26" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B15" s="24"/>
       <c r="C15" s="24"/>
@@ -1691,7 +1696,7 @@
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A16" s="29" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B16" s="29"/>
       <c r="C16" s="29"/>
@@ -1989,7 +1994,7 @@
     </row>
     <row r="24" ht="18" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A24" s="29" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B24" s="29"/>
       <c r="C24" s="29"/>
@@ -2065,7 +2070,7 @@
     </row>
     <row r="26" ht="18" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A26" s="26" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26" s="24"/>
       <c r="C26" s="24"/>
@@ -2585,7 +2590,7 @@
     </row>
     <row r="40" ht="17.1" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A40" s="35" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B40" s="35"/>
       <c r="C40" s="35"/>
@@ -2595,7 +2600,7 @@
       <c r="G40" s="36"/>
       <c r="H40" s="37"/>
       <c r="I40" s="37" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J40" s="37"/>
       <c r="K40" s="37"/>
@@ -2634,7 +2639,7 @@
       <c r="G41" s="39"/>
       <c r="H41" s="34"/>
       <c r="I41" s="34" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J41" s="34"/>
       <c r="K41" s="34"/>
@@ -2665,7 +2670,7 @@
     </row>
     <row r="42" ht="17.1" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A42" s="35" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B42" s="35"/>
       <c r="C42" s="35"/>
@@ -2675,7 +2680,7 @@
       <c r="G42" s="36"/>
       <c r="H42" s="37"/>
       <c r="I42" s="37" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J42" s="37"/>
       <c r="K42" s="37"/>
@@ -2747,7 +2752,7 @@
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
@@ -2819,7 +2824,7 @@
     </row>
     <row r="46" ht="13.5" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A46" s="26" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B46" s="24"/>
       <c r="C46" s="44"/>
@@ -2858,7 +2863,7 @@
     </row>
     <row r="47" ht="13.5" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A47" s="26" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B47" s="24"/>
       <c r="C47" s="44"/>
@@ -2897,7 +2902,7 @@
     </row>
     <row r="48" ht="13.5" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A48" s="26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B48" s="24"/>
       <c r="C48" s="44"/>
@@ -2936,7 +2941,7 @@
     </row>
     <row r="49" ht="13.5" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A49" s="26" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B49" s="24"/>
       <c r="C49" s="44"/>
@@ -2976,7 +2981,7 @@
     <row r="50" ht="13.5" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A50" s="26"/>
       <c r="B50" s="18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C50" s="18"/>
       <c r="D50" s="18"/>
@@ -3052,7 +3057,7 @@
     <row r="52" ht="13.5" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A52" s="26"/>
       <c r="B52" s="47" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C52" s="47"/>
       <c r="D52" s="47"/>
@@ -3128,7 +3133,7 @@
     <row r="54" ht="13.5" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A54" s="26"/>
       <c r="B54" s="49" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C54" s="49"/>
       <c r="D54" s="49"/>
@@ -3167,7 +3172,7 @@
     <row r="55" ht="15.95" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A55" s="26"/>
       <c r="B55" s="18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C55" s="18"/>
       <c r="D55" s="18"/>
@@ -3280,7 +3285,7 @@
     <row r="58" ht="15.95" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A58" s="26"/>
       <c r="B58" s="18" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C58" s="18"/>
       <c r="D58" s="18"/>
@@ -3356,7 +3361,7 @@
     <row r="60" ht="13.5" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A60" s="26"/>
       <c r="B60" s="18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C60" s="18"/>
       <c r="D60" s="18"/>
@@ -3395,7 +3400,7 @@
     <row r="61" ht="13.5" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A61" s="26"/>
       <c r="B61" s="18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C61" s="18"/>
       <c r="D61" s="18"/>
@@ -3470,7 +3475,7 @@
     </row>
     <row r="63" ht="13.5" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A63" s="26" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B63" s="24"/>
       <c r="C63" s="44"/>
@@ -3990,7 +3995,7 @@
     </row>
     <row r="77" ht="13.5" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A77" s="26" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B77" s="24"/>
       <c r="C77" s="44"/>
@@ -4029,7 +4034,7 @@
     </row>
     <row r="78" ht="13.5" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A78" s="26" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B78" s="24"/>
       <c r="C78" s="44"/>
@@ -4068,7 +4073,7 @@
     </row>
     <row r="79" ht="13.5" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A79" s="26" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B79" s="24"/>
       <c r="C79" s="44"/>
@@ -4107,7 +4112,7 @@
     </row>
     <row r="80" ht="13.5" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A80" s="26" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B80" s="24"/>
       <c r="C80" s="44"/>
@@ -4183,7 +4188,7 @@
     </row>
     <row r="82" ht="13.5" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A82" s="26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B82" s="24"/>
       <c r="C82" s="44"/>
@@ -4223,7 +4228,7 @@
     <row r="83" ht="13.5" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A83" s="26"/>
       <c r="B83" s="24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C83" s="44"/>
       <c r="D83" s="44"/>
@@ -4262,7 +4267,7 @@
     <row r="84" ht="13.5" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A84" s="26"/>
       <c r="B84" s="24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C84" s="44"/>
       <c r="D84" s="44"/>
@@ -4301,7 +4306,7 @@
     <row r="85" ht="13.5" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A85" s="26"/>
       <c r="B85" s="24" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C85" s="44"/>
       <c r="D85" s="44"/>
@@ -4340,7 +4345,7 @@
     <row r="86" ht="13.5" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A86" s="26"/>
       <c r="B86" s="24" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C86" s="44"/>
       <c r="D86" s="44"/>
@@ -4379,7 +4384,7 @@
     <row r="87" ht="13.5" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A87" s="26"/>
       <c r="B87" s="24" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C87" s="44"/>
       <c r="D87" s="44"/>
@@ -4418,7 +4423,7 @@
     <row r="88" ht="13.5" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A88" s="26"/>
       <c r="B88" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C88" s="44"/>
       <c r="D88" s="44"/>
@@ -4457,7 +4462,7 @@
     <row r="89" ht="13.5" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A89" s="26"/>
       <c r="B89" s="24" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C89" s="44"/>
       <c r="D89" s="44"/>
@@ -4496,7 +4501,7 @@
     <row r="90" ht="13.5" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A90" s="26"/>
       <c r="B90" s="24" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C90" s="44"/>
       <c r="D90" s="44"/>
@@ -4535,7 +4540,7 @@
     <row r="91" ht="13.5" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A91" s="26"/>
       <c r="B91" s="24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C91" s="44"/>
       <c r="D91" s="44"/>
@@ -4574,7 +4579,7 @@
     <row r="92" ht="13.5" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A92" s="26"/>
       <c r="B92" s="24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C92" s="44"/>
       <c r="D92" s="44"/>
@@ -4613,7 +4618,7 @@
     <row r="93" ht="13.5" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A93" s="26"/>
       <c r="B93" s="24" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C93" s="44"/>
       <c r="D93" s="44"/>
